--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/03-test-cases/CYC-3-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/03-test-cases/CYC-3-test-cases.xlsx
@@ -392,7 +392,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-05T16:27:31.724Z</t>
+    <t>2026-10-05T16:44:19.403Z</t>
   </si>
   <si>
     <t>Column order</t>
